--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-04-2026.xlsx
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£27.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£41.23</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '1,191.35'</t>
+          <t>£14296.2</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>£56.23</t>
+          <t>£54.65</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>£54.47</t>
+          <t>£58.97</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>£52.68</t>
+          <t>£53.95</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>£1248.0</t>
+          <t>£1378.56</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>£1328.0</t>
+          <t>£1540.32</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>£1280.0</t>
+          <t>£1467.52</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
